--- a/artfynd/A 54769-2020 artfynd.xlsx
+++ b/artfynd/A 54769-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127455210</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>127455238</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54769-2020 artfynd.xlsx
+++ b/artfynd/A 54769-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127455210</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>127455238</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54769-2020 artfynd.xlsx
+++ b/artfynd/A 54769-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127455210</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>127455238</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54769-2020 artfynd.xlsx
+++ b/artfynd/A 54769-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127455210</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>127455238</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
